--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N49_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N49_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.54026558037602</v>
+        <v>6.262793156811104</v>
       </c>
       <c r="D2" t="n">
-        <v>38.56394223369242</v>
+        <v>6.266640612975018</v>
       </c>
       <c r="E2" t="n">
-        <v>10.63877707014655</v>
+        <v>1.728801273898815</v>
       </c>
       <c r="F2" t="n">
-        <v>9.388599524405917</v>
+        <v>1.525647422715962</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>31.33059757665326</v>
+        <v>5.091222106206156</v>
       </c>
       <c r="D3" t="n">
-        <v>31.26453022964058</v>
+        <v>5.080486162316595</v>
       </c>
       <c r="E3" t="n">
-        <v>10.63877707014655</v>
+        <v>1.728801273898815</v>
       </c>
       <c r="F3" t="n">
-        <v>9.388599524405917</v>
+        <v>1.525647422715962</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>10.0164824366409</v>
+        <v>1.627678395954146</v>
       </c>
       <c r="D4" t="n">
-        <v>13.66163679660705</v>
+        <v>2.220015979448645</v>
       </c>
       <c r="E4" t="n">
-        <v>10.63877707014655</v>
+        <v>1.728801273898815</v>
       </c>
       <c r="F4" t="n">
-        <v>9.388599524405917</v>
+        <v>1.525647422715962</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.50192035700701</v>
+        <v>3.656562058013639</v>
       </c>
       <c r="D5" t="n">
-        <v>33.58354833125173</v>
+        <v>5.457326603828406</v>
       </c>
       <c r="E5" t="n">
-        <v>10.63877707014655</v>
+        <v>1.728801273898815</v>
       </c>
       <c r="F5" t="n">
-        <v>9.388599524405917</v>
+        <v>1.525647422715962</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
